--- a/downloads/Bachelor_of_Technology_Electrical_Engineering_SEMESTER_-_4_Summer_2025__Regular_SEM_4_08_09_2025.xlsx
+++ b/downloads/Bachelor_of_Technology_Electrical_Engineering_SEMESTER_-_4_Summer_2025__Regular_SEM_4_08_09_2025.xlsx
@@ -657,7 +657,7 @@
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" s="9" t="n"/>
@@ -684,7 +684,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>sedf</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>First year</t>
+          <t>Second year</t>
         </is>
       </c>
       <c r="I7" s="12" t="n"/>
@@ -707,7 +707,7 @@
       <c r="M7" s="14" t="n"/>
       <c r="N7" s="15" t="inlineStr">
         <is>
-          <t>00 | OCT 01, 2025</t>
+          <t>00 | OCT 03, 2025</t>
         </is>
       </c>
       <c r="O7" s="14" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>sdf</t>
+          <t>ELECTRICAL ENGG</t>
         </is>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -734,7 +734,7 @@
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>sdf</t>
+          <t>123298</t>
         </is>
       </c>
       <c r="I8" s="16" t="n"/>
@@ -904,61 +904,61 @@
       <c r="C12" s="18" t="n"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>ff</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E12" s="18" t="n"/>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G12" s="18" t="n"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="I12" s="18" t="n"/>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Bhoopesh Chaudhari</t>
         </is>
       </c>
       <c r="K12" s="18" t="n"/>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="M12" s="18" t="n"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="O12" s="18" t="n"/>
       <c r="P12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="Q12" s="18" t="n"/>
       <c r="R12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>g</t>
         </is>
       </c>
       <c r="S12" s="18" t="n"/>
       <c r="T12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U12" s="18" t="n"/>
       <c r="V12" s="17" t="inlineStr">
         <is>
-          <t>f</t>
+          <t xml:space="preserve">Me </t>
         </is>
       </c>
       <c r="W12" s="18" t="n"/>
